--- a/arista/dist/20261025_Arista模型_v0.1.1.xlsx
+++ b/arista/dist/20261025_Arista模型_v0.1.1.xlsx
@@ -3444,7 +3444,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -3681,7 +3681,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -3802,7 +3802,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -3923,7 +3923,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4044,7 +4044,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4165,7 +4165,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
